--- a/AAII_Financials/Quarterly/GARPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GARPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="92">
   <si>
     <t>GARPY</t>
   </si>
@@ -656,48 +656,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45747</v>
       </c>
       <c r="G7" s="2">
         <v>45657</v>
@@ -712,22 +712,25 @@
         <v>45107</v>
       </c>
       <c r="K7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,8 +770,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,8 +814,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -849,8 +858,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -866,8 +878,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -907,8 +920,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,8 +964,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -989,8 +1008,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1030,8 +1052,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,8 +1069,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1085,8 +1111,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,8 +1155,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1143,8 +1175,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1184,8 +1217,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1225,8 +1261,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1266,8 +1305,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1307,8 +1349,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1348,8 +1393,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1389,8 +1437,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1430,8 +1481,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1471,8 +1525,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1512,8 +1569,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,8 +1613,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1594,8 +1657,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1635,8 +1701,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1676,8 +1745,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1717,8 +1789,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1758,8 +1833,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1799,24 +1877,27 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45747</v>
       </c>
       <c r="G38" s="2">
         <v>45657</v>
@@ -1831,22 +1912,25 @@
         <v>45107</v>
       </c>
       <c r="K38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1862,8 +1946,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1879,16 +1964,17 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>404100</v>
+      </c>
+      <c r="E41" s="3">
         <v>523400</v>
-      </c>
-      <c r="E41" s="3">
-        <v>471000</v>
       </c>
       <c r="F41" s="3">
         <v>471000</v>
@@ -1906,30 +1992,33 @@
         <v>557100</v>
       </c>
       <c r="K41" s="3">
+        <v>557100</v>
+      </c>
+      <c r="L41" s="3">
         <v>691100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>557100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>691100</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>735900</v>
+      </c>
+      <c r="E42" s="3">
         <v>621100</v>
-      </c>
-      <c r="E42" s="3">
-        <v>574600</v>
       </c>
       <c r="F42" s="3">
         <v>574600</v>
@@ -1947,30 +2036,33 @@
         <v>643500</v>
       </c>
       <c r="K42" s="3">
+        <v>643500</v>
+      </c>
+      <c r="L42" s="3">
         <v>454000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>643500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>454000</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1044200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1017200</v>
-      </c>
-      <c r="E43" s="3">
-        <v>983500</v>
       </c>
       <c r="F43" s="3">
         <v>983500</v>
@@ -1988,30 +2080,33 @@
         <v>659800</v>
       </c>
       <c r="K43" s="3">
+        <v>659800</v>
+      </c>
+      <c r="L43" s="3">
         <v>903000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>659800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>903000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2164600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1854200</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1964900</v>
       </c>
       <c r="F44" s="3">
         <v>1964900</v>
@@ -2029,30 +2124,33 @@
         <v>1434400</v>
       </c>
       <c r="K44" s="3">
+        <v>1434400</v>
+      </c>
+      <c r="L44" s="3">
         <v>1570400</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>1434400</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>1570400</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>520600</v>
+      </c>
+      <c r="E45" s="3">
         <v>298900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>448800</v>
       </c>
       <c r="F45" s="3">
         <v>448800</v>
@@ -2070,30 +2168,33 @@
         <v>536500</v>
       </c>
       <c r="K45" s="3">
+        <v>536500</v>
+      </c>
+      <c r="L45" s="3">
         <v>404900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>536500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>404900</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5183400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4555100</v>
-      </c>
-      <c r="E46" s="3">
-        <v>4653200</v>
       </c>
       <c r="F46" s="3">
         <v>4653200</v>
@@ -2111,30 +2212,33 @@
         <v>4086800</v>
       </c>
       <c r="K46" s="3">
+        <v>4086800</v>
+      </c>
+      <c r="L46" s="3">
         <v>4158500</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>4086800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>4158500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1854900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1829100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1737800</v>
       </c>
       <c r="F47" s="3">
         <v>1737800</v>
@@ -2152,30 +2256,33 @@
         <v>1569700</v>
       </c>
       <c r="K47" s="3">
+        <v>1569700</v>
+      </c>
+      <c r="L47" s="3">
         <v>1519400</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>1569700</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>1519400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4029000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3907500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3857600</v>
       </c>
       <c r="F48" s="3">
         <v>3857600</v>
@@ -2193,30 +2300,33 @@
         <v>3794600</v>
       </c>
       <c r="K48" s="3">
+        <v>3794600</v>
+      </c>
+      <c r="L48" s="3">
         <v>3820300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>3794600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>3820300</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>151700</v>
+      </c>
+      <c r="E49" s="3">
         <v>150600</v>
-      </c>
-      <c r="E49" s="3">
-        <v>150300</v>
       </c>
       <c r="F49" s="3">
         <v>150300</v>
@@ -2234,22 +2344,25 @@
         <v>165900</v>
       </c>
       <c r="K49" s="3">
+        <v>165900</v>
+      </c>
+      <c r="L49" s="3">
         <v>167900</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>165900</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>167900</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2289,8 +2402,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2330,16 +2446,19 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E52" s="3">
         <v>149400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>182000</v>
       </c>
       <c r="F52" s="3">
         <v>182000</v>
@@ -2357,22 +2476,25 @@
         <v>104200</v>
       </c>
       <c r="K52" s="3">
+        <v>104200</v>
+      </c>
+      <c r="L52" s="3">
         <v>100400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>104200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>100400</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2412,16 +2534,19 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11435400</v>
+      </c>
+      <c r="E54" s="3">
         <v>10665400</v>
-      </c>
-      <c r="E54" s="3">
-        <v>10665800</v>
       </c>
       <c r="F54" s="3">
         <v>10665800</v>
@@ -2439,22 +2564,25 @@
         <v>9851800</v>
       </c>
       <c r="K54" s="3">
+        <v>9851800</v>
+      </c>
+      <c r="L54" s="3">
         <v>9902100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>9851800</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>9902100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2470,8 +2598,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2487,16 +2616,17 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1018700</v>
+      </c>
+      <c r="E57" s="3">
         <v>358700</v>
-      </c>
-      <c r="E57" s="3">
-        <v>718300</v>
       </c>
       <c r="F57" s="3">
         <v>718300</v>
@@ -2514,30 +2644,33 @@
         <v>456400</v>
       </c>
       <c r="K57" s="3">
+        <v>456400</v>
+      </c>
+      <c r="L57" s="3">
         <v>431400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>456400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>431400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2047400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2085600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1883200</v>
       </c>
       <c r="F58" s="3">
         <v>1883200</v>
@@ -2555,30 +2688,33 @@
         <v>1665500</v>
       </c>
       <c r="K58" s="3">
+        <v>1665500</v>
+      </c>
+      <c r="L58" s="3">
         <v>2001000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1665500</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>2001000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>673500</v>
+      </c>
+      <c r="E59" s="3">
         <v>591600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>512600</v>
       </c>
       <c r="F59" s="3">
         <v>512600</v>
@@ -2596,30 +2732,33 @@
         <v>372600</v>
       </c>
       <c r="K59" s="3">
+        <v>372600</v>
+      </c>
+      <c r="L59" s="3">
         <v>557300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>372600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3967100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3259800</v>
-      </c>
-      <c r="E60" s="3">
-        <v>3316900</v>
       </c>
       <c r="F60" s="3">
         <v>3316900</v>
@@ -2637,30 +2776,33 @@
         <v>2692700</v>
       </c>
       <c r="K60" s="3">
+        <v>2692700</v>
+      </c>
+      <c r="L60" s="3">
         <v>3193900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>2692700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>3193900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1463300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1445900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1482000</v>
       </c>
       <c r="F61" s="3">
         <v>1482000</v>
@@ -2678,30 +2820,33 @@
         <v>1434300</v>
       </c>
       <c r="K61" s="3">
+        <v>1434300</v>
+      </c>
+      <c r="L61" s="3">
         <v>1139900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1434300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>1139900</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1900</v>
       </c>
       <c r="F62" s="3">
         <v>1900</v>
@@ -2719,22 +2864,25 @@
         <v>900</v>
       </c>
       <c r="K62" s="3">
+        <v>900</v>
+      </c>
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2774,8 +2922,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2815,8 +2966,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2856,16 +3010,19 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5655800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4938400</v>
-      </c>
-      <c r="E66" s="3">
-        <v>5157700</v>
       </c>
       <c r="F66" s="3">
         <v>5157700</v>
@@ -2883,22 +3040,25 @@
         <v>4512500</v>
       </c>
       <c r="K66" s="3">
+        <v>4512500</v>
+      </c>
+      <c r="L66" s="3">
         <v>4647700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>4512500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>4647700</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2914,8 +3074,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2955,8 +3116,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2996,8 +3160,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3037,8 +3204,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3078,16 +3248,19 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4243700</v>
+      </c>
+      <c r="E72" s="3">
         <v>4171000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3931000</v>
       </c>
       <c r="F72" s="3">
         <v>3931000</v>
@@ -3105,22 +3278,25 @@
         <v>3521400</v>
       </c>
       <c r="K72" s="3">
+        <v>3521400</v>
+      </c>
+      <c r="L72" s="3">
         <v>3433000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>3521400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>3433000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3160,8 +3336,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3201,8 +3380,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3242,16 +3424,19 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5455900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5415100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5216700</v>
       </c>
       <c r="F76" s="3">
         <v>5216700</v>
@@ -3269,22 +3454,25 @@
         <v>5090700</v>
       </c>
       <c r="K76" s="3">
+        <v>5090700</v>
+      </c>
+      <c r="L76" s="3">
         <v>5001500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>5090700</v>
       </c>
       <c r="M76" s="3">
         <v>5090700</v>
       </c>
       <c r="N76" s="3">
-        <v>5001500</v>
+        <v>5090700</v>
       </c>
       <c r="O76" s="3">
         <v>5001500</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3">
+        <v>5001500</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3324,24 +3512,27 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45747</v>
       </c>
       <c r="G80" s="2">
         <v>45657</v>
@@ -3356,22 +3547,25 @@
         <v>45107</v>
       </c>
       <c r="K80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3411,8 +3605,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3428,8 +3625,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3469,8 +3667,11 @@
       <c r="O83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3510,8 +3711,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3755,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3592,8 +3799,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3633,8 +3843,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3674,19 +3887,22 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="3">
-        <v>316100</v>
-      </c>
-      <c r="F89" s="3">
-        <v>316100</v>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>4</v>
@@ -3715,8 +3931,11 @@
       <c r="O89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3732,19 +3951,20 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="3">
-        <v>-91200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-91200</v>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
@@ -3773,8 +3993,11 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3814,8 +4037,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3855,19 +4081,22 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
-        <v>-83800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-83800</v>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>4</v>
@@ -3896,8 +4125,11 @@
       <c r="O94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3913,19 +4145,20 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>39200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>39200</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>4</v>
@@ -3954,8 +4187,11 @@
       <c r="O96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3995,8 +4231,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4036,8 +4275,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4077,19 +4319,22 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
-        <v>-234200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-234200</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>4</v>
@@ -4118,8 +4363,11 @@
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4159,8 +4407,11 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4168,10 +4419,10 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
@@ -4188,8 +4439,8 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
@@ -4198,6 +4449,9 @@
         <v>4</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
